--- a/artfynd/A 27985-2026 artfynd.xlsx
+++ b/artfynd/A 27985-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1024139</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1473280</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1473281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938301</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938302</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938304</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938305</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938306</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938307</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3938309</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2050,6 +2115,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939259</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939260</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939261</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939262</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2474,6 +2559,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939263</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2580,6 +2670,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3939267</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2686,6 +2781,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4241708</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967977</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967980</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3004,6 +3114,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967982</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967983</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3216,6 +3336,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967984</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3322,6 +3447,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967985</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3428,6 +3558,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967986</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3534,6 +3669,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967987</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3640,6 +3780,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967988</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3746,6 +3891,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967989</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3852,6 +4002,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967990</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3958,6 +4113,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967991</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4064,6 +4224,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967992</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4170,6 +4335,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4967993</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4276,6 +4446,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968251</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4382,6 +4557,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968252</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4488,6 +4668,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968253</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4594,6 +4779,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968254</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4700,6 +4890,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968255</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4806,6 +5001,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968256</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4912,6 +5112,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968268</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5018,6 +5223,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968269</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5124,6 +5334,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968284</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5230,6 +5445,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968508</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5336,6 +5556,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4968509</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5442,8 +5667,60 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5288896</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>